--- a/annotation_folder/annotated_results-nat.xlsx
+++ b/annotation_folder/annotated_results-nat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nataliechu/Desktop/CPSC 554/project/project_repo/annotation_folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D52BD0-DD40-CB4D-90DA-E7E37B8F0BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B834904-B542-864C-A444-4E3E494B69B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="1080" windowWidth="41380" windowHeight="24600" xr2:uid="{678AFF50-194E-1844-9CF1-2C4B0496FC60}"/>
+    <workbookView xWindow="9780" yWindow="1760" windowWidth="37920" windowHeight="20780" xr2:uid="{678AFF50-194E-1844-9CF1-2C4B0496FC60}"/>
   </bookViews>
   <sheets>
     <sheet name="annotated_results-nat" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="373">
   <si>
     <t>Complaint ID</t>
   </si>
@@ -62,9 +62,6 @@
     <t>c1_score</t>
   </si>
   <si>
-    <t>c1_label</t>
-  </si>
-  <si>
     <t>c1_evidence_quotes</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
   </si>
   <si>
     <t>c4_score</t>
-  </si>
-  <si>
-    <t>c4_label</t>
   </si>
   <si>
     <t>c4_evidence_quotes</t>
@@ -1211,15 +1205,9 @@
     <t>c0_label</t>
   </si>
   <si>
-    <t>c0_evidence quotes</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
-    <t>Not accessible</t>
-  </si>
-  <si>
     <t>Frustration</t>
   </si>
   <si>
@@ -1229,21 +1217,12 @@
     <t>Intensified language and rhetorical escalation</t>
   </si>
   <si>
-    <t>online transfers and transactions</t>
-  </si>
-  <si>
     <t xml:space="preserve">I purchased an item that was misrepresented to me… I sent the item back to the seller...I expected a refund at that point. </t>
   </si>
   <si>
     <t>I paid for an item that was not as it was advertised and not acceptable to me and has been returned</t>
   </si>
   <si>
-    <t xml:space="preserve">make a META account with my name...they have hacked into my personal XXXX...i had a unknown login attempt </t>
-  </si>
-  <si>
-    <t>High perceived vulnerability</t>
-  </si>
-  <si>
     <t>Embarassment</t>
   </si>
   <si>
@@ -1256,18 +1235,12 @@
     <t>ended up losing {$2100.00}. This was just about everything I had at that time</t>
   </si>
   <si>
-    <t xml:space="preserve">someone had tried to open an account with my information...the person had hacked my XXXX account </t>
-  </si>
-  <si>
     <t>Sometimes i can change the password...i cant 100 % remove the hackerbecause he has two factor authetnication on my profile and somehow got it verfied that its him/her…</t>
   </si>
   <si>
     <t xml:space="preserve">someone had tried to open an account with my information. Once I informed them it was not me, they then told me the person had hacked my XXXX account and was trying to make two transfers….In order to reverse these transfers, I had to follow his instructions which were to enter the amount and " send '' money </t>
   </si>
   <si>
-    <t>low perceived vulnerability</t>
-  </si>
-  <si>
     <t>Regret</t>
   </si>
   <si>
@@ -1280,15 +1253,9 @@
     <t>self blame or counterfactual language</t>
   </si>
   <si>
-    <t>No digital asset engagement</t>
-  </si>
-  <si>
     <t xml:space="preserve">In order to reverse these transfers, I had to follow his instructions which were to enter the amount and " send '' money...with a special code in the memo… I did this from both my checking and savings account and ended up losing {$2100.00}. </t>
   </si>
   <si>
-    <t>My savings account of {$4000.00} was externally compromised</t>
-  </si>
-  <si>
     <t>I found Wells Fargo was the victim of a data breach in XX/XX/XXXX ( when this theft occurred. ) However, Wells Fargo never acknowledged this. Instead, they made a final decision and closed my case.</t>
   </si>
   <si>
@@ -1308,9 +1275,6 @@
   </si>
   <si>
     <t>The perpetrator fraudulently transferred {$4000.00} from my savings account - to my checking account.</t>
-  </si>
-  <si>
-    <t>unauthorized ACH payment that was debited from my XXXX XXXX account XXXX in the amount of {$140000.00}, which I discovered to have been processed through American Express.</t>
   </si>
   <si>
     <t>leaving me in a vulnerable position without the recovery of my lost funds...This situation is especially distressing as I am currently XXXXXXXX XXXX in service to our country, which makes it even more difficult to address these matters in person</t>
@@ -1326,15 +1290,9 @@
 These legal challenges are indicative of a pattern of behavior that directly impacts my experience with Cash App. I feel that my rights as a consumer have been violated, and Cash App has not demonstrated a sufficient commitment to consumer protection. </t>
   </si>
   <si>
-    <t>Anger, Vengence</t>
-  </si>
-  <si>
     <t xml:space="preserve">...convinced me to help them send money for some antiques they were supposedly getting and needed to make a down payment on. I foolishly agreed to help and while they told me they had wired a transfer over it had not come in so they sent me a check to deposit and than send through PayPal. </t>
   </si>
   <si>
-    <t>not accessible</t>
-  </si>
-  <si>
     <t>After doing so it hit me how foolish it was and I did what I could to undo the action….. I was not aware that money laundering had gotten so advanced and want to help others from falling for the same traps that I did</t>
   </si>
   <si>
@@ -1356,9 +1314,6 @@
     <t>, I have encountered significant difficulties in accessing and managing my funds, including cryptocurrency holdings...I am a verified XXXX user who has followed all required identification and verification processes as outlined by the platform...preventing me from transferring cryptocurrency to my personal cold storage wallet</t>
   </si>
   <si>
-    <t>digital asset engagement</t>
-  </si>
-  <si>
     <t xml:space="preserve">The lack of responsiveness from XXXX customer support team, combined with the ongoing restriction of my account, has caused me significant distress and financial harm...I am requesting that the CFPB take immediate action to ensure that XXXX resolves this issue, lifts the restrictions on my account, and compensates affected customers for the financial harm </t>
   </si>
   <si>
@@ -1374,9 +1329,6 @@
     <t xml:space="preserve">I made my last authorized transaction on my Coinbase account, which was a send transaction of XXXX XXXX. Shortly after, a series of unauthorized transactions took place, </t>
   </si>
   <si>
-    <t>Vengence</t>
-  </si>
-  <si>
     <t>justice-seeking language</t>
   </si>
   <si>
@@ -1386,15 +1338,9 @@
     <t>the following unauthorized transactions occurred : XXXX. Send Transactions ( Unauthorized XXXXXXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXX XXXXXXXX ( {$4800.00} USD ) XXXXXXXX XXXX sent to XXXX ( {$980.00} USD ) XXXXXXXX XXXX sent to XXXX ( {$2800.00} USD ) XXXX XXXX sent to XXXX ( {$2100.00} USD ) XXXX. Buy &amp; Sell Transactions ( Unauthorized Trading Activity ) : Purchased XXXX XXXX  for {$2000.00} USD Sold XXXX XXXX  for {$2000.00} USD Purchased XXXX XXXX  for {$4800.00} USD Sold XXXX XXXX  for {$4800.00} USD Purchased XXXX XXXX  for {$1200.00} USD Purchased XXXX XXXX  for {$600.00} USD I did not authorize any of these transactions, and they indicate that my account was accessed by an unauthorized party</t>
   </si>
   <si>
-    <t>account credentials</t>
-  </si>
-  <si>
     <t>I did not authorize any of these transactions, and they indicate that my account was accessed by an unauthorized party. At the time, all devices used to access my Coinbase account were in my possession. I have not experienced any SIM swap, phone service interruption, phishing emails, or malware infections on my devices.</t>
   </si>
   <si>
-    <t>personal identification</t>
-  </si>
-  <si>
     <t xml:space="preserve">my social security number was used to collect money through Cash App..., I was told they would forward the information to their fraud department and asked me to provide information... did I give my information to anyone. </t>
   </si>
   <si>
@@ -1407,9 +1353,6 @@
     <t xml:space="preserve">my social security number was used to collect money through Cash App in XXXX. Square , Inc. sent a total of XXXX 1099-Bs to the IRS. </t>
   </si>
   <si>
-    <t>no digital asset engagement</t>
-  </si>
-  <si>
     <t>I would like to request that I be paid back the {$1100.00} that was wrongfully taken from me and denied insurance or coverage via XXXXChase.</t>
   </si>
   <si>
@@ -1419,9 +1362,6 @@
     <t xml:space="preserve">I already froze my account for the 3 major credit bureaus approximately 5 months ago, but somehow Cash App allowed an individual to open an account and debit card under my name without my consent. I have already filed a police report notifying them of the identity theft incident as well...I read online that a lot of people were encountering the same thing where they received a Cash App debit card without opening ones themselves and with most not even having used Cash App like myself. This is not an isolated incident and Cash App needs to address this problem of fraud and identity theft that persist with their company and using compromised information to open the accounts of unsuspecting victims. </t>
   </si>
   <si>
-    <t>moderate perceived vulnerability</t>
-  </si>
-  <si>
     <t>Vengeance</t>
   </si>
   <si>
@@ -1476,9 +1416,6 @@
     <t>I was recently banking with Citibank so I had a checking and savings account with them but I also had XXXX XXXX XXXX  so I transferred two XXXX dollars withdrawals from my XXXX XXXX XXXX  to Citibank which made that XXXX dollars on the XXXX of XXXX so it wasnt never available too me in Citibank</t>
   </si>
   <si>
-    <t>personal possesions</t>
-  </si>
-  <si>
     <t>The USAA imposter provided me personal information about my credit card and banking info, 3-digit code, home address, and were sending text messages that were coming from USAA.</t>
   </si>
   <si>
@@ -1563,9 +1500,6 @@
     <t xml:space="preserve"> I ended up loosing about {$450.00} between the money they scammed me out of from cash app by doing tests and they kept trying larger amounts </t>
   </si>
   <si>
-    <t>online transfers and transcations</t>
-  </si>
-  <si>
     <t>a fraudulent transaction occurred on my account, resulting in a charge of {$860.00} for a purchase I never received</t>
   </si>
   <si>
@@ -1590,9 +1524,6 @@
     <t>I was so upset about being hacked on my accounts, I decided to call Bank of America to see how this could have happened. I wanted to take additional steps to protect my account...this person had all of my information, I contacted the credit bureaus and locked my information. I also got a pin for my taxes. I changed all my passwords.</t>
   </si>
   <si>
-    <t>high perceived vulnerability</t>
-  </si>
-  <si>
     <t>I told him how this is a crazy amount of money to me and people kill themselves for less and this is how bank of America chooses to treat their people</t>
   </si>
   <si>
@@ -1617,9 +1548,6 @@
     <t>I immediately emailed back to Truist Alerts that I had not sent out any payments. I contacted Truist and told them this {$5000.00} was a fraud.</t>
   </si>
   <si>
-    <t>behavioural characteristics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Over the course of XXXX thru XXXX. We text and talked on the phone almost daily. </t>
   </si>
   <si>
@@ -1632,12 +1560,6 @@
     <t xml:space="preserve">I met someone on a XXXX website called XXXX...He asked if I could loan him money until he got back to XXXX  to deposit his insurance check and at that time he would reimbursement me….I went to my bank, which is XXXX XXXX, and got a cashiers check for that amount. I then went to Bank of America for a wire transfer. </t>
   </si>
   <si>
-    <t>personal possesios</t>
-  </si>
-  <si>
-    <t>severe perceived vulnerability</t>
-  </si>
-  <si>
     <t xml:space="preserve">, i have a mental illness, I also have XXXX XXXX XXXX XXXX XXXX XXXX XXXXXXXX XXXX XXXXXXXX XXXX. XXXX also XXXX XXXX XXXX and XXXX, living on XXXX which is very little. What they stole from me was more than half of my check. </t>
   </si>
   <si>
@@ -1654,6 +1576,195 @@
   </si>
   <si>
     <t>XXXX XXXX 's failure to do so caused me to a financial injury in the amount of {$84000.00} as well as threats of being harmed by a convicted criminal, TD Bank and its criminal bank employees and customer/s which has caused financial and emotional distress to me and my family that will last us a lifetime.</t>
+  </si>
+  <si>
+    <t>Sadness</t>
+  </si>
+  <si>
+    <t>we find both unreasonable and unethical, especially considering the circumstances of the initial issue and the prompt repayment. This decision effectively cuts off all electronic communication and financial support for our loved one, which is devastating not only to him but to us as a family trying to stay connected during his incarceration.</t>
+  </si>
+  <si>
+    <t>This flag has made it impossible for us to deposit funds to his commissary or prison tablet...This situation has caused our family undue emotional and financial distress</t>
+  </si>
+  <si>
+    <t>inadvertently closed a checking account that had been used to make a {$100.00} payment to my brothers JPay account. As soon as we became aware of this mistake, both my mother and grandmother repaid the amount in full via XXXX,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The e-mails that I now know to be fraudulent directed me to pay 60 % of the total cost as a deposit before work could be scheduled, and mentioned that they accepted Zelle and wire transfer. </t>
+  </si>
+  <si>
+    <t>I now believe that their XXXX e-mail was hacked and this bad actor intercepted our communication and targeted me. The e-mails appeared legitimate because they originated from their same e-mail address and stayed within the thread that was already in progress from my XXXX When I view the metadata for the e-mails, they do appear suspicious, but they bypassed the XXXX phishing filters.</t>
+  </si>
+  <si>
+    <t>The other person whose name and number were used for the fraud could also be a victim of identity theft if they are not the perpetrator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am seeking restitution, purity damages, and mental anguish for the lost funds...what theyre doing is messing up my credit that I work so hard to build up how you have a credit score </t>
+  </si>
+  <si>
+    <t>Ive come along way for the people to come here and call themselves robbing me. By paying for something that I already paid for. not only that they added a bunch of miscellaneous charges on top of my bills so I just feel like this is just wrong and something need to be done about this.</t>
+  </si>
+  <si>
+    <t>I was misled into authorizing a payment of amount {$990.00} to an individual criminals name XXXX XXXX XXXX or alias XXXX XXXX through the use of my fingerprint authentication.</t>
+  </si>
+  <si>
+    <t>I am now left with nothing. I do not own the business, I received no value in return, and I am being denied access to the funds because the banks involved will not take basic corrective action.</t>
+  </si>
+  <si>
+    <t>Anger, Vengeance</t>
+  </si>
+  <si>
+    <t>This transaction should never have gone through. If either bank had followed standard compliance protocolsand the check had been rejected as it should have beenI would have known the business was not legally operational, and the transaction would have never occurred. Their failure to flag or reject this check directly enabled a fraudulent sale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I obtained a cashiers check from Chase Bank for {$80000.00}, made payable to XXXX XXXX XXXX XXXX XXXX XXXXXXXX as part of a business purchase... This means the business I believed I was purchasing could not legally exist or operate, even if reinstatement were attempted. Despite this, XXXX XXXX  accepted and deposited the check into an account that should have been closed since XXXX issue XXXX has since acknowledged directly. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">my XXXX was wrapped into XXXX and moved to the XXXX blockchain. These assets were then converted into various XXXX-based tokens and used across XXXX  protocols, custodial exchanges, and staking platforms. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Despite my many attempts to revoke permissions, reset devices, secure my network, and contact support teams, I have received no meaningful resolution. My iCloud, email, and browser identities have also been compromised in tandem with these attacks. Even paid services like XXXX, XXXX, XXXX, and XXXX were repeatedly infiltrated. </t>
+  </si>
+  <si>
+    <t>This is a coordinated financial abuse involving wallet hijacking, unauthorized custodianship, stolen royalties, and synthetic identity creation, all profiting off assets that were originally mine and never consented to for investment, lending, or redistribution</t>
+  </si>
+  <si>
+    <t>These platforms have profited from stolen, restaked, and relabeled assets tied to my legal identity and private holdings.</t>
+  </si>
+  <si>
+    <t>He told me to keep him on the line and put my phone in my pocket and let him know when the {$9000.00} transaction was complete. ( I put my phone on the Tellers counter ) I asked the Teller to withdraw {$9000.00} from my checking account</t>
+  </si>
+  <si>
+    <t>He told me my XXXX XXXX account was set up wrong, and he would help me set up a secure account. He said he closed out my current debit card, and a new one would be issued is 5-7 days. ..He needed the code that was just sent to me to start the process. I gave him the code. He needed the second and third codes also that were sent to me. I gave that to him!...I called the REAL Wells Fargo fraud company immediately while I was at the bank and met with the banker XXXX XXXX XXXX savings, checking and debit card was closed immediately. I filed a claim with Wells Fargo immediately</t>
+  </si>
+  <si>
+    <t>I asked her If you had {$10000.00} fraudulently taken out of your account, would you just accept the claim being closed?...I also asked her where is my protection, keeping my money in a Wells Fargo bank. I told her that I thought Wells Fargo had insurance to protect their customers!</t>
+  </si>
+  <si>
+    <t>I will keep fighting to get my money back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">highly unfair and financially damaging transaction dispute in which I, as a seller, was deprived of both payment and property with no recourse provided and no protection under PayPals Seller Protection policy, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct sale, payment made via PayPal </t>
+  </si>
+  <si>
+    <t>Reimburse me the {$740.00} I am owed for the item, or recover the item from the buyer. Explain why the buyer was allowed to keep the item without returning it.</t>
+  </si>
+  <si>
+    <t>I believe I should be compensated {$400.00} immediately thats it thats all I want is my {$400.00}</t>
+  </si>
+  <si>
+    <t>I believe I should be compensated {$400.00} immediately thats it thats all I want is my {$400.00} XXXX understand that they may be upset because I figured out a way to use their promo to get it. I didnt do anything illegal deceptive nothing I just looked into all of them...I am using this as a first attempt to avoid court</t>
+  </si>
+  <si>
+    <t>The scammer instructed me to send money through XXXX and PayPal under the pretense that it was required to receive a larger sum in return. I followed the instructions in good faith, but I never received any funds or services</t>
+  </si>
+  <si>
+    <t>I am requesting a full reimbursement under Regulation E and an investigation into Bank of Americas failure to properly evaluate a clearly documented fraud case.</t>
+  </si>
+  <si>
+    <t>I was targeted in an online scam where I was falsely promised a financial transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I received fraudulent emails impersonating Zelle, and he introduced a second layer of the scam by pretending to be a Zelle customer service rep. He used very convincing language and repeatedly said we were on a recorded line to appear legitimate. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">He claimed he sent me a {$1100.00} payment through Zelle and that in order to receive it, I needed to upgrade my account to a business profile. I received fraudulent emails impersonating Zelle, and he introduced a second layer of the scam by pretending to be a Zelle customer service rep. He used very convincing language and repeatedly said we were on a recorded line to appear legitimate....When I attempted to send the {$500.00} via Zelle, I received a notification from XXXX that there was a problem processing the payment. </t>
+  </si>
+  <si>
+    <t>While it is true that I completed the transactions, I did so under fraudulent manipulation and deception. I was coerced and misled, believing I was acting on behalf of my employer</t>
+  </si>
+  <si>
+    <t>I followed their instructions and completed XXXX money transfers using my Apple Card via the XXXX XXXX mobile application</t>
+  </si>
+  <si>
+    <t>I am requesting CFPB support to investigate this fraud and hold Zelle accountable for enabling scams without consumer protection</t>
+  </si>
+  <si>
+    <t>this was clearly a case of impersonation, fraud, and social engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was coerced and misled, believing I was acting on behalf of my employer...I was clearly a victim of a scam </t>
+  </si>
+  <si>
+    <t xml:space="preserve">we exchanged numbers and chatted via XXXX...provided log in details for banking information to XXXX XXXX XXXX Bank where I logged in to send a transfer to his supplier on his behalf...I was also had been sending emails on his behalf to an email address ( XXXX ) at the bank that turned out to be fake to confirm receipt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I logged in to send a transfer to his supplier on his behalf, which was successful. The amount transferred was in millions of dollars as the account has over XXXX dollars in it.... To obtain a new code, an amount of over XXXX USD had to be paid to Chase bank. I sent the first installments on XX/XX/XXXX for XXXXXXXX XXXX and then on XX/XX/XXXX for XXXXXXXX XXXX through global money transfer...I made installments via global money transfer from my bank for XXXX XXXX on XX/XX/year&gt;, then the same amount on XX/XX/XXXX, and again on XX/XX/year&gt;. The last amount transferred was for XXXXXXXX XXXX  on XX/XX/year&gt;. </t>
+  </si>
+  <si>
+    <t>The only contact information I have of this person are the following : Phone number : XXXX Email : XXXX XXXX</t>
+  </si>
+  <si>
+    <t>We have been asking for status updates from XXXXXXXX XXXX  daily, but their response is always the same - that they've heard nothing from Citizens Bank despite multiple requests for updates. We reached out to Citizens Bank ; they told us they only help their customers and to talk to our bank. We called XXXX XXXX  headquarters ; they told us they can't help us and to talk to the local branch...I feel we are getting the run-around from both banks. In the meantime, more time elapses and we are less and less likely to recover any of the funds.</t>
+  </si>
+  <si>
+    <t>the email was fraudulent and immediately called XXXX XXXX to recall the wire transfe</t>
+  </si>
+  <si>
+    <t>we received a request from the XXXX  ( via email ) to send the next payment ( {$250000.00}, the largest payment to date ) to a new account</t>
+  </si>
+  <si>
+    <t>I first came across this investment opportunity through what looked like a legitimate XXXX account for XXXX XXXX. I made initial contact in XX/XX/XXXX and continued talking with him in XX/XX/XXXX. This scammer utilized a fraudulent website named XXXX XXXX. This happened while another scammer named XXXX XXXX reached out to me. He utilized a fraudulent website named XXXX XXXX. Both scams involved exchange platforms like XXXX and XXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This was a substantial financial blow to my savings...My banks and exchange platforms were not helpful to me in recovering these funds and even caused me more stress and mental health pressure. This is while Im still a college student and do not have any stable source of income yet. </t>
+  </si>
+  <si>
+    <t>The purpose of this claim encompasses two key objectives. Firstly, it is intended to establish that a breach of the duty of care has occurred, primarily stemming from multiple exchanges platforms failure to conduct thorough due diligence and/or exercise reasonable and prudent judgment in preventing foreseeable and substantial damages that I have incurred due to fraudulent activities. Secondly, it serves as an official written request for reimbursement, grounded in the reasons mentioned above, among other supporting factors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im simply asking for access to my funds after proving my identity beyond a reasonable doubt. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I find this deeply unfair and possibly abusive, as Ive made every effort to comply with their process and regain access...Why should Paxful require ID verification when creating account and then deny when you try to verify with that same ID </t>
+  </si>
+  <si>
+    <t>important quantity of money that I earned working hard just for somebody to try to take advantage of my values taught in the military.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I couldn't notice because the fake account told me that it was a new account he had to make because his phone got broken and that he was talking to me through a computer, and that he needed money for a family emergency. </t>
+  </si>
+  <si>
+    <t>I was so stupid for sending that quantity of money...I tried to do a good action and ended up getting tricked and played</t>
+  </si>
+  <si>
+    <t>I sent two payments through my PayPal account totaling XXXX to someone named XXXX XXXX XXXX XXXX at XXXX</t>
+  </si>
+  <si>
+    <t>I have a record of that communication. Despite this, PayPal refused to intervene, citing their policy that personal payments are not covered under Purchase Protection. That response ignored the full context and failed to take any action to stop fraud, even when I reported it in real time...I am now asking the CFPB to hold PayPal accountable as well. PayPal allowed this scam to succeed and ignored my attempts to stop it, even though they had the tools and the notice to act</t>
+  </si>
+  <si>
+    <t>I sent two payments through my PayPal account totaling XXXX to someone named XXXX XXXX XXXX XXXX at XXXX. I now know that I was being scammed</t>
+  </si>
+  <si>
+    <t>I followed her instructions. In order to fix the process and regain control of my accounts I needed to first go to the Official XXXX XXXX XXXX XXXXnline and download this program that can find out where theyre getting access to my money from and hopefully recover it. so I went to the XXXX XXXX XXXX  on my phone and I downloaded the app since it was from the actual XXXX XXXX  and they were claiming to be the XXXX fraud department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They basically took all of my personal money I had in my account. I get it wasnt much money at all, but its all I have and a crime was committed against me...I know $XXXX  is not a lot of money to a lot of people but it was everything to me </t>
+  </si>
+  <si>
+    <t>Sadness, Shame</t>
+  </si>
+  <si>
+    <t>He saw I was very upset and asked what was going on and I told him and he was devastated...I was crying and I was upset and I was scared and I was violated...Im not getting anywhere and I feel like after being scammed and taking advantage of my bank tells me theyre gonna help me and when the time comes, they dont they just help themselves...I feel like a XXXX  for believing that that was really XXXX  and I feel like a fool for trusting Bank of America to do what they said they would do help please any help please.</t>
+  </si>
+  <si>
+    <t>..I continued to listen to her instructions to stop the thieves from taking everything I have. But the program apparently let them find a back door into my phone, where they could see my phone in real time without me knowing they were...I gave her no usernames and I gave her no passwords. She could just see my phone exactly the way I was seeing it. She did that so that they could go into my bank accounts &amp; steal my money &amp; the companys money...I could get to Bank of America and have everything locked down like pinnacle was able to.</t>
+  </si>
+  <si>
+    <t>the real estate agents email was compromised…</t>
+  </si>
+  <si>
+    <t>I received a email from the person who had compromised the email stating to wire the closing cost by sending it to a XXXX XXXX  account</t>
+  </si>
+  <si>
+    <t>About an hour after I wired the money we realized that it was a fraud and Capital One issued a wire transfer recall to get back the mone</t>
+  </si>
+  <si>
+    <t>The money is still sitting at XXXX XXXX  and I have been waiting for XXXX XXXX. I opened a case with the police as well. On XX/XX/XXXX Capital One tried recall the money back again and they still have not responded...This lack of communication and resolution has caused me considerable concern</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2276,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2198,9 +2309,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2581,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F0D2FF-6877-8847-A803-7C390B57B552}">
-  <dimension ref="A1:Y101"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -2592,24 +2700,21 @@
     <col min="7" max="7" width="255.83203125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="35.33203125" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="67.1640625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="45.33203125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="29.5" style="5" customWidth="1"/>
-    <col min="20" max="20" width="33.33203125" style="5" customWidth="1"/>
-    <col min="21" max="21" width="33.83203125" style="5" customWidth="1"/>
-    <col min="22" max="22" width="40.1640625" style="5" customWidth="1"/>
-    <col min="23" max="23" width="40.6640625" customWidth="1"/>
-    <col min="24" max="24" width="26" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="78.6640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="67.1640625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="45.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="29.5" style="5" customWidth="1"/>
+    <col min="18" max="18" width="33.33203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="33.83203125" style="5" customWidth="1"/>
+    <col min="20" max="20" width="40.1640625" style="5" customWidth="1"/>
+    <col min="21" max="21" width="40.6640625" customWidth="1"/>
+    <col min="22" max="22" width="78.6640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2635,58 +2740,49 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
       <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="P1" s="5" t="s">
+        <v>259</v>
+      </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>280</v>
+        <v>183</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>184</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>186</v>
+        <v>14</v>
+      </c>
+      <c r="U1" t="s">
+        <v>15</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="W1" t="s">
         <v>16</v>
       </c>
-      <c r="X1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="306" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:22" ht="306" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>11380835</v>
       </c>
@@ -2694,73 +2790,64 @@
         <v>45661</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="H2">
         <v>542</v>
       </c>
       <c r="I2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="P2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="R2" s="5">
+        <v>2</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="J2" t="s">
-        <v>189</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="T2" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="R2" s="5">
-        <v>1</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="T2" s="5">
-        <v>2</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="102" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>11415830</v>
       </c>
@@ -2768,19 +2855,19 @@
         <v>45664</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H3">
         <v>317</v>
@@ -2788,29 +2875,29 @@
       <c r="I3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K3">
+      <c r="J3">
         <v>3</v>
       </c>
-      <c r="L3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>204</v>
+      <c r="K3" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="12">
+        <v>0</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
-      <c r="O3" s="12">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
+      <c r="O3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="R3" s="5">
         <v>1</v>
@@ -2818,26 +2905,17 @@
       <c r="S3" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="T3" s="5">
-        <v>1</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>208</v>
+      <c r="T3" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="238" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="238" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>11565628</v>
       </c>
@@ -2845,19 +2923,19 @@
         <v>45673</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="H4">
         <v>419</v>
@@ -2865,56 +2943,47 @@
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>206</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>205</v>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>2100</v>
       </c>
       <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4" s="3">
-        <v>2100</v>
-      </c>
-      <c r="P4">
         <v>3</v>
       </c>
+      <c r="O4" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1</v>
+      </c>
       <c r="Q4" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="R4" s="5">
-        <v>1</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="T4" s="5">
-        <v>2</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="409.6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>11577188</v>
       </c>
@@ -2922,19 +2991,19 @@
         <v>45673</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="H5">
         <v>622</v>
@@ -2942,56 +3011,47 @@
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T5" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P5">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="R5" s="5">
-        <v>1</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T5" s="5">
-        <v>2</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y5" s="10" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="356" x14ac:dyDescent="0.2">
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="356" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>11600288</v>
       </c>
@@ -2999,19 +3059,19 @@
         <v>45678</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="H6">
         <v>626</v>
@@ -3019,56 +3079,47 @@
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>190</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>23</v>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>2</v>
-      </c>
-      <c r="O6" s="3">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>219</v>
+        <v>321</v>
       </c>
       <c r="R6" s="5">
         <v>2</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="T6" s="5">
-        <v>2</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y6" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="372" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" s="10" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="372" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>11743531</v>
       </c>
@@ -3076,19 +3127,19 @@
         <v>45681</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>469</v>
@@ -3096,56 +3147,47 @@
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>190</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>23</v>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" s="11">
+        <v>100000</v>
       </c>
       <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7" s="11">
-        <v>100000</v>
-      </c>
-      <c r="P7">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="R7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T7" s="5">
-        <v>2</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T7" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="Y7" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="136" x14ac:dyDescent="0.2">
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>11799736</v>
       </c>
@@ -3153,19 +3195,19 @@
         <v>45684</v>
       </c>
       <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H8">
         <v>451</v>
@@ -3173,56 +3215,47 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>190</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>23</v>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>227</v>
+        <v>0</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="P8" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="R8" s="5">
         <v>2</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="T8" s="5">
-        <v>2</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>230</v>
+        <v>216</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
       </c>
       <c r="V8" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y8" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="409.6" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>11811866</v>
       </c>
@@ -3230,19 +3263,19 @@
         <v>45686</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H9">
         <v>605</v>
@@ -3250,56 +3283,47 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>190</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>23</v>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3">
+        <v>11000</v>
       </c>
       <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9" s="3">
-        <v>11000</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>233</v>
+        <v>0</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="R9" s="5">
         <v>2</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="T9" s="5">
-        <v>2</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>239</v>
+        <v>224</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y9" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="409.6" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>11817372</v>
       </c>
@@ -3307,19 +3331,19 @@
         <v>45686</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="H10">
         <v>637</v>
@@ -3327,56 +3351,47 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>190</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>23</v>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>2</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10">
         <v>3</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>234</v>
+      <c r="O10" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="R10" s="5">
         <v>2</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="T10" s="5">
-        <v>2</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>239</v>
+        <v>224</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="W10">
-        <v>2</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y10" s="9" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="272" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="272" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>11818430</v>
       </c>
@@ -3384,19 +3399,19 @@
         <v>45685</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H11">
         <v>329</v>
@@ -3404,57 +3419,48 @@
       <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
-        <v>206</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11" s="12">
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="12">
         <f>4800+2800+980+2100+2000+2000+4800+4800+1200+600</f>
         <v>26080</v>
       </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>245</v>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="R11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="T11" s="5">
-        <v>2</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>243</v>
+        <v>227</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y11" s="9" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="255" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="255" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11830388</v>
       </c>
@@ -3462,19 +3468,19 @@
         <v>45686</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H12">
         <v>378</v>
@@ -3482,56 +3488,47 @@
       <c r="I12">
         <v>2</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>206</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>249</v>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3">
+        <v>22000</v>
       </c>
       <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="R12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T12" s="5">
-        <v>2</v>
-      </c>
-      <c r="U12" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="Y12" s="9" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="356" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="356" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11879178</v>
       </c>
@@ -3539,19 +3536,19 @@
         <v>45688</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H13">
         <v>821</v>
@@ -3559,56 +3556,47 @@
       <c r="I13">
         <v>2</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13" t="s">
-        <v>206</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>290</v>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3">
+        <v>3700</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
-      <c r="O13" s="3">
-        <v>3700</v>
-      </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>254</v>
+      <c r="O13" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="R13" s="5">
         <v>2</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="T13" s="5">
-        <v>2</v>
-      </c>
-      <c r="U13" s="5" t="s">
-        <v>293</v>
+        <v>272</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="W13">
-        <v>1</v>
-      </c>
-      <c r="X13" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="153" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>11922222</v>
       </c>
@@ -3616,19 +3604,19 @@
         <v>45693</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H14">
         <v>477</v>
@@ -3636,56 +3624,47 @@
       <c r="I14">
         <v>2</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K14">
-        <v>2</v>
-      </c>
-      <c r="L14" t="s">
-        <v>257</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>256</v>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
+      <c r="O14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>23</v>
+        <v>238</v>
       </c>
       <c r="R14" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="T14" s="5">
-        <v>2</v>
-      </c>
-      <c r="U14" s="5" t="s">
-        <v>243</v>
+        <v>227</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
       </c>
       <c r="V14" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="Y14" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="409.6" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11966797</v>
       </c>
@@ -3693,19 +3672,19 @@
         <v>45694</v>
       </c>
       <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>21</v>
-      </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H15">
         <v>420</v>
@@ -3713,56 +3692,47 @@
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>190</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>23</v>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>263</v>
+        <v>1</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="R15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T15" s="5">
-        <v>2</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V15" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="W15">
-        <v>1</v>
-      </c>
-      <c r="X15" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y15" s="8" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="388" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="388" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12106732</v>
       </c>
@@ -3770,19 +3740,19 @@
         <v>45705</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H16">
         <v>685</v>
@@ -3790,56 +3760,47 @@
       <c r="I16">
         <v>1</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="N16">
+        <v>4</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R16" s="5">
+        <v>2</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s">
-        <v>206</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="P16">
-        <v>4</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="R16" s="5">
-        <v>1</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T16" s="5">
-        <v>2</v>
-      </c>
-      <c r="U16" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V16" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="W16">
-        <v>1</v>
-      </c>
-      <c r="X16" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y16" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="356" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:22" ht="356" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>12137899</v>
       </c>
@@ -3847,19 +3808,19 @@
         <v>45707</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H17">
         <v>359</v>
@@ -3867,56 +3828,47 @@
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>190</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>23</v>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>269</v>
+        <v>1</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="P17" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="R17" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="T17" s="5">
-        <v>2</v>
-      </c>
-      <c r="U17" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="V17" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="W17">
-        <v>2</v>
-      </c>
-      <c r="X17" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y17" s="8" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="102" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="U17">
+        <v>2</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>12171804</v>
       </c>
@@ -3924,19 +3876,19 @@
         <v>45709</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H18">
         <v>364</v>
@@ -3944,56 +3896,47 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>190</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>23</v>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>2</v>
-      </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18">
         <v>3</v>
       </c>
-      <c r="Q18" s="14" t="s">
-        <v>271</v>
+      <c r="O18" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="P18" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="R18" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="T18" s="5">
-        <v>2</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>274</v>
+        <v>254</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y18" s="9" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="409.6" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>12201830</v>
       </c>
@@ -4001,19 +3944,19 @@
         <v>45714</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="H19">
         <v>498</v>
@@ -4021,45 +3964,36 @@
       <c r="I19">
         <v>3</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>190</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>277</v>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1000</v>
       </c>
       <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="R19" s="5">
-        <v>0</v>
-      </c>
-      <c r="V19" s="13"/>
-      <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y19" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="372" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="13"/>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="372" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>12367566</v>
       </c>
@@ -4067,19 +4001,19 @@
         <v>45723</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H20">
         <v>602</v>
@@ -4087,56 +4021,47 @@
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K20">
-        <v>2</v>
-      </c>
-      <c r="L20" t="s">
-        <v>257</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>281</v>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2900</v>
       </c>
       <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="R20" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="T20" s="5">
-        <v>2</v>
-      </c>
-      <c r="U20" s="5" t="s">
-        <v>284</v>
+        <v>263</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
       </c>
       <c r="V20" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="W20">
-        <v>1</v>
-      </c>
-      <c r="X20" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y20" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="323" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="323" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>12394663</v>
       </c>
@@ -4144,19 +4069,19 @@
         <v>45726</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="F21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="H21">
         <v>666</v>
@@ -4164,56 +4089,47 @@
       <c r="I21" s="15">
         <v>0</v>
       </c>
-      <c r="J21" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="15">
-        <v>0</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>23</v>
+      <c r="J21" s="15">
+        <v>0</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1050</v>
       </c>
       <c r="N21">
         <v>1</v>
       </c>
-      <c r="O21" s="3">
-        <v>1050</v>
-      </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>287</v>
+      <c r="O21" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="P21" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="R21" s="5">
         <v>2</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="T21" s="5">
-        <v>2</v>
-      </c>
-      <c r="U21" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="V21" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="W21">
-        <v>1</v>
-      </c>
-      <c r="X21" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y21" s="9" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="323" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="T21" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="323" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>12405276</v>
       </c>
@@ -4221,19 +4137,19 @@
         <v>45726</v>
       </c>
       <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
         <v>19</v>
       </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
       <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="H22">
         <v>375</v>
@@ -4241,53 +4157,44 @@
       <c r="I22" s="15">
         <v>0</v>
       </c>
-      <c r="J22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="15">
-        <v>0</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>190</v>
+      <c r="J22" s="15">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3">
+        <v>600</v>
       </c>
       <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22" s="3">
-        <v>600</v>
-      </c>
-      <c r="P22">
         <v>3</v>
       </c>
+      <c r="O22" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="P22" s="5">
+        <v>1</v>
+      </c>
       <c r="Q22" s="5" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="R22" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="T22" s="5">
-        <v>2</v>
-      </c>
-      <c r="U22" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="V22" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="W22">
-        <v>1</v>
-      </c>
-      <c r="X22" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y22" s="8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="289" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+      <c r="T22" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="289" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>12413240</v>
       </c>
@@ -4295,19 +4202,19 @@
         <v>45728</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="H23">
         <v>321</v>
@@ -4315,56 +4222,47 @@
       <c r="I23">
         <v>3</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23" t="s">
-        <v>206</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>297</v>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3">
+        <v>3200</v>
       </c>
       <c r="N23">
         <v>1</v>
       </c>
-      <c r="O23" s="3">
-        <v>3200</v>
-      </c>
-      <c r="P23">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>298</v>
+      <c r="O23" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="P23" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="R23" s="5">
         <v>1</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="T23" s="5">
-        <v>1</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>243</v>
+        <v>227</v>
+      </c>
+      <c r="T23" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="U23">
+        <v>2</v>
       </c>
       <c r="V23" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="W23">
-        <v>2</v>
-      </c>
-      <c r="X23" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y23" s="9" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="323" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="323" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>12515275</v>
       </c>
@@ -4372,19 +4270,19 @@
         <v>45733</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H24">
         <v>692</v>
@@ -4392,56 +4290,47 @@
       <c r="I24">
         <v>3</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24" t="s">
-        <v>206</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>303</v>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3">
+        <v>450</v>
       </c>
       <c r="N24">
         <v>1</v>
       </c>
-      <c r="O24" s="3">
-        <v>450</v>
-      </c>
-      <c r="P24">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>304</v>
+      <c r="O24" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P24" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="R24" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T24" s="5">
-        <v>2</v>
-      </c>
-      <c r="U24" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
       </c>
       <c r="V24" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="X24" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y24" s="9" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="238" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="238" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>12567633</v>
       </c>
@@ -4449,19 +4338,19 @@
         <v>45735</v>
       </c>
       <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
         <v>19</v>
       </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H25">
         <v>441</v>
@@ -4469,56 +4358,47 @@
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>228</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>306</v>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4">
+        <v>860</v>
       </c>
       <c r="N25">
         <v>1</v>
       </c>
-      <c r="O25" s="4">
-        <v>860</v>
-      </c>
-      <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>308</v>
+      <c r="O25" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="P25" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="R25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="T25" s="5">
-        <v>2</v>
-      </c>
-      <c r="U25" s="5" t="s">
-        <v>239</v>
+        <v>224</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="W25">
-        <v>1</v>
-      </c>
-      <c r="X25" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="Y25" s="9" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="119" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>12576357</v>
       </c>
@@ -4526,19 +4406,19 @@
         <v>45736</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H26">
         <v>413</v>
@@ -4546,56 +4426,47 @@
       <c r="I26">
         <v>2</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K26">
+      <c r="J26">
         <v>3</v>
       </c>
-      <c r="L26" t="s">
-        <v>198</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>311</v>
+      <c r="K26" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26">
         <v>4</v>
       </c>
-      <c r="Q26" s="9" t="s">
-        <v>310</v>
+      <c r="O26" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="P26" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="R26" s="5">
         <v>2</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="T26" s="5">
-        <v>2</v>
-      </c>
-      <c r="U26" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y26" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="409.6" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="T26" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>12614082</v>
       </c>
@@ -4603,19 +4474,19 @@
         <v>45738</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="F27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="H27">
         <v>3248</v>
@@ -4623,56 +4494,47 @@
       <c r="I27">
         <v>3</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K27">
+      <c r="J27">
         <v>3</v>
       </c>
-      <c r="L27" t="s">
-        <v>314</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>313</v>
+      <c r="K27" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3">
+        <v>5500</v>
       </c>
       <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27" s="3">
-        <v>5500</v>
-      </c>
-      <c r="P27">
         <v>3</v>
       </c>
-      <c r="Q27" s="9" t="s">
-        <v>315</v>
+      <c r="O27" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="P27" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="R27" s="5">
         <v>2</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="T27" s="5">
-        <v>2</v>
-      </c>
-      <c r="U27" s="5" t="s">
-        <v>316</v>
+        <v>293</v>
+      </c>
+      <c r="T27" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
       </c>
       <c r="V27" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="W27">
-        <v>1</v>
-      </c>
-      <c r="X27" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y27" s="9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" ht="238" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="238" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>12657751</v>
       </c>
@@ -4680,19 +4542,19 @@
         <v>45741</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H28">
         <v>468</v>
@@ -4700,56 +4562,47 @@
       <c r="I28">
         <v>1</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28" t="s">
-        <v>190</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>319</v>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3">
+        <v>5000</v>
       </c>
       <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="O28" s="3">
-        <v>5000</v>
-      </c>
-      <c r="P28">
-        <v>2</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>320</v>
+        <v>2</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="P28" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="R28" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T28" s="5">
-        <v>2</v>
-      </c>
-      <c r="U28" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
       </c>
       <c r="V28" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y28" s="9" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" ht="119" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>12687179</v>
       </c>
@@ -4757,19 +4610,19 @@
         <v>45743</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H29">
         <v>301</v>
@@ -4777,56 +4630,47 @@
       <c r="I29">
         <v>4</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29" t="s">
-        <v>190</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>324</v>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29" s="17">
+        <v>150000</v>
       </c>
       <c r="N29">
         <v>1</v>
       </c>
-      <c r="O29" s="18">
-        <v>150000</v>
-      </c>
-      <c r="P29">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>325</v>
+      <c r="O29" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="P29" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="R29" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T29" s="5">
-        <v>2</v>
-      </c>
-      <c r="U29" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V29" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="W29">
-        <v>1</v>
-      </c>
-      <c r="X29" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y29" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="153" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>12821239</v>
       </c>
@@ -4834,19 +4678,19 @@
         <v>45751</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H30">
         <v>501</v>
@@ -4854,50 +4698,41 @@
       <c r="I30">
         <v>3</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="K30">
+      <c r="J30">
         <v>4</v>
       </c>
-      <c r="L30" t="s">
-        <v>329</v>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3">
+        <v>480</v>
       </c>
       <c r="N30">
-        <v>1</v>
-      </c>
-      <c r="O30" s="3">
-        <v>480</v>
-      </c>
-      <c r="P30">
         <v>3</v>
       </c>
-      <c r="Q30" s="9" t="s">
-        <v>330</v>
+      <c r="O30" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="P30" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="R30" s="5">
         <v>1</v>
       </c>
-      <c r="S30" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="T30" s="5">
-        <v>1</v>
-      </c>
-      <c r="V30" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y30" s="9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="T30" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>13100288</v>
       </c>
@@ -4905,19 +4740,19 @@
         <v>45768</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H31">
         <v>2488</v>
@@ -4925,50 +4760,44 @@
       <c r="I31" s="15">
         <v>0</v>
       </c>
-      <c r="J31" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" s="15">
-        <v>0</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>190</v>
+      <c r="J31" s="15">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18">
+        <v>84000</v>
       </c>
       <c r="N31">
-        <v>1</v>
-      </c>
-      <c r="O31" s="19">
-        <v>84000</v>
-      </c>
-      <c r="P31">
         <v>3</v>
       </c>
-      <c r="Q31" s="9" t="s">
-        <v>335</v>
+      <c r="O31" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="P31" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="R31" s="5">
         <v>2</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="U31" s="5" t="s">
-        <v>239</v>
+        <v>224</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y31" s="9" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" ht="306" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="306" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>13250261</v>
       </c>
@@ -4976,26 +4805,64 @@
         <v>45777</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E32" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="F32" t="s">
-        <v>85</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="H32">
         <v>383</v>
       </c>
-      <c r="O32" s="4"/>
-    </row>
-    <row r="33" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+      <c r="I32" s="15">
+        <v>0</v>
+      </c>
+      <c r="J32" s="15">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="P32" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="R32" s="5">
+        <v>2</v>
+      </c>
+      <c r="S32" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="T32" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>13437981</v>
       </c>
@@ -5003,26 +4870,64 @@
         <v>45786</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H33">
         <v>398</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="1:15" ht="170" x14ac:dyDescent="0.2">
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="R33" s="5">
+        <v>2</v>
+      </c>
+      <c r="S33" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="T33" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="U33">
+        <v>2</v>
+      </c>
+      <c r="V33" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>13497965</v>
       </c>
@@ -5030,26 +4935,64 @@
         <v>45790</v>
       </c>
       <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
         <v>19</v>
       </c>
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" t="s">
-        <v>21</v>
-      </c>
       <c r="F34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H34">
         <v>583</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="1:15" ht="323" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34" s="3">
+        <v>990</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="P34" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="R34" s="5">
+        <v>2</v>
+      </c>
+      <c r="S34" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="T34" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="323" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>13530102</v>
       </c>
@@ -5057,26 +5000,64 @@
         <v>45793</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H35">
         <v>390</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="36" spans="1:15" ht="356" x14ac:dyDescent="0.2">
+      <c r="I35" s="15">
+        <v>0</v>
+      </c>
+      <c r="J35" s="15">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35" s="3">
+        <v>80000</v>
+      </c>
+      <c r="N35">
+        <v>4</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="P35" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R35" s="5">
+        <v>2</v>
+      </c>
+      <c r="S35" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T35" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="356" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>13546522</v>
       </c>
@@ -5084,25 +5065,67 @@
         <v>45793</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H36">
         <v>469</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I36" s="15">
+        <v>2</v>
+      </c>
+      <c r="J36" s="15">
+        <v>2</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="P36" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R36" s="5">
+        <v>2</v>
+      </c>
+      <c r="S36" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T36" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="U36">
+        <v>2</v>
+      </c>
+      <c r="V36" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>13562702</v>
       </c>
@@ -5110,26 +5133,67 @@
         <v>45793</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H37">
         <v>768</v>
       </c>
-      <c r="O37" s="3"/>
-    </row>
-    <row r="38" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I37" s="15">
+        <v>1</v>
+      </c>
+      <c r="J37" s="15">
+        <v>1</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="P37" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="R37" s="5">
+        <v>2</v>
+      </c>
+      <c r="S37" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T37" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>13582132</v>
       </c>
@@ -5137,26 +5201,65 @@
         <v>45796</v>
       </c>
       <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
         <v>19</v>
       </c>
-      <c r="D38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" t="s">
-        <v>21</v>
-      </c>
       <c r="F38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H38">
         <v>558</v>
       </c>
-      <c r="O38" s="3"/>
-    </row>
-    <row r="39" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I38" s="15">
+        <v>0</v>
+      </c>
+      <c r="J38" s="15">
+        <v>0</v>
+      </c>
+      <c r="K38" s="8"/>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3">
+        <v>740</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="P38" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="R38" s="5">
+        <v>2</v>
+      </c>
+      <c r="S38" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="T38" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38" s="8" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>13586171</v>
       </c>
@@ -5164,26 +5267,61 @@
         <v>45796</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="F39" t="s">
-        <v>96</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="H39">
         <v>833</v>
       </c>
-      <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="1:15" ht="204" x14ac:dyDescent="0.2">
+      <c r="I39" s="15">
+        <v>0</v>
+      </c>
+      <c r="J39" s="15">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" s="3">
+        <v>400</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="P39" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R39" s="5">
+        <v>2</v>
+      </c>
+      <c r="S39" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T39" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="204" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>13627370</v>
       </c>
@@ -5191,25 +5329,64 @@
         <v>45797</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H40">
         <v>347</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="272" x14ac:dyDescent="0.2">
+      <c r="I40" s="15">
+        <v>0</v>
+      </c>
+      <c r="J40" s="15">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="P40" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R40" s="5">
+        <v>2</v>
+      </c>
+      <c r="S40" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T40" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="272" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>13821247</v>
       </c>
@@ -5217,26 +5394,67 @@
         <v>45808</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H41">
         <v>322</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="1:15" ht="356" x14ac:dyDescent="0.2">
+      <c r="I41" s="15">
+        <v>2</v>
+      </c>
+      <c r="J41" s="15">
+        <v>1</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="P41" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R41" s="5">
+        <v>2</v>
+      </c>
+      <c r="S41" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T41" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="356" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>13900795</v>
       </c>
@@ -5244,26 +5462,65 @@
         <v>45812</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H42">
         <v>387</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="1:15" ht="187" x14ac:dyDescent="0.2">
+      <c r="I42" s="15">
+        <v>0</v>
+      </c>
+      <c r="J42" s="15">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42" s="3">
+        <f>1800+1400</f>
+        <v>3200</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="P42" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="R42" s="5">
+        <v>2</v>
+      </c>
+      <c r="S42" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="T42" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="204" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>13972297</v>
       </c>
@@ -5271,22 +5528,55 @@
         <v>45818</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H43">
         <v>626</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" ht="204" x14ac:dyDescent="0.2">
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>3</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="P43" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R43" s="5">
+        <v>2</v>
+      </c>
+      <c r="S43" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T43" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="U43">
+        <v>2</v>
+      </c>
+      <c r="V43" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="204" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>14033520</v>
       </c>
@@ -5294,26 +5584,64 @@
         <v>45821</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H44">
         <v>345</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I44" s="15">
+        <v>0</v>
+      </c>
+      <c r="J44" s="15">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44" s="3">
+        <v>250000</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="P44" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R44" s="5">
+        <v>2</v>
+      </c>
+      <c r="S44" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T44" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44" s="9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>14037359</v>
       </c>
@@ -5321,25 +5649,64 @@
         <v>45820</v>
       </c>
       <c r="C45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H45">
         <v>1038</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I45" s="15">
+        <v>0</v>
+      </c>
+      <c r="J45" s="15">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45" s="18">
+        <v>30000</v>
+      </c>
+      <c r="N45">
+        <v>3</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="P45" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R45" s="5">
+        <v>2</v>
+      </c>
+      <c r="S45" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T45" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="U45">
+        <v>2</v>
+      </c>
+      <c r="V45" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>14038074</v>
       </c>
@@ -5347,25 +5714,64 @@
         <v>45820</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F46" t="s">
+        <v>102</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="H46">
         <v>1038</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" ht="221" x14ac:dyDescent="0.2">
+      <c r="I46" s="15">
+        <v>0</v>
+      </c>
+      <c r="J46" s="15">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46" s="18">
+        <v>30000</v>
+      </c>
+      <c r="N46">
+        <v>3</v>
+      </c>
+      <c r="O46" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="P46" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R46" s="5">
+        <v>2</v>
+      </c>
+      <c r="S46" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T46" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="U46">
+        <v>2</v>
+      </c>
+      <c r="V46" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="221" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14045811</v>
       </c>
@@ -5373,22 +5779,59 @@
         <v>45821</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H47">
         <v>360</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" ht="170" x14ac:dyDescent="0.2">
+      <c r="I47" s="15">
+        <v>0</v>
+      </c>
+      <c r="J47" s="15">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47" s="12">
+        <f>5500+150</f>
+        <v>5650</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P47" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="R47" s="5">
+        <v>2</v>
+      </c>
+      <c r="S47" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="T47" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>14066893</v>
       </c>
@@ -5396,26 +5839,64 @@
         <v>45821</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H48">
         <v>621</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+      <c r="I48" s="15">
+        <v>0</v>
+      </c>
+      <c r="J48" s="15">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N48">
+        <v>2</v>
+      </c>
+      <c r="O48" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="P48" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="R48" s="5">
+        <v>2</v>
+      </c>
+      <c r="S48" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="T48" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" s="9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="187" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>14069656</v>
       </c>
@@ -5423,25 +5904,64 @@
         <v>45821</v>
       </c>
       <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
         <v>19</v>
       </c>
-      <c r="D49" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" t="s">
-        <v>21</v>
-      </c>
       <c r="F49" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H49">
         <v>440</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I49" s="15">
+        <v>0</v>
+      </c>
+      <c r="J49" s="15">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>2</v>
+      </c>
+      <c r="M49" s="12">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="P49" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="R49" s="5">
+        <v>2</v>
+      </c>
+      <c r="S49" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="T49" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="V49" s="9" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>14173829</v>
       </c>
@@ -5449,25 +5969,64 @@
         <v>45827</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H50">
         <v>1522</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" ht="238" x14ac:dyDescent="0.2">
+      <c r="I50" s="15">
+        <v>3</v>
+      </c>
+      <c r="J50" s="15">
+        <v>2</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50" s="12">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>2</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="P50" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="R50" s="5">
+        <v>1</v>
+      </c>
+      <c r="T50" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="U50">
+        <v>2</v>
+      </c>
+      <c r="V50" s="9" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="238" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>14290687</v>
       </c>
@@ -5475,25 +6034,67 @@
         <v>45833</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H51">
         <v>406</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" ht="119" x14ac:dyDescent="0.2">
+      <c r="I51" s="15">
+        <v>3</v>
+      </c>
+      <c r="J51" s="15">
+        <v>0</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
+      <c r="M51" s="12">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R51" s="5">
+        <v>2</v>
+      </c>
+      <c r="S51" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T51" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>14340534</v>
       </c>
@@ -5501,25 +6102,25 @@
         <v>45835</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H52">
         <v>343</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="187" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" ht="187" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>14426777</v>
       </c>
@@ -5527,25 +6128,25 @@
         <v>45840</v>
       </c>
       <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
         <v>19</v>
       </c>
-      <c r="D53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" t="s">
-        <v>21</v>
-      </c>
       <c r="F53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H53">
         <v>571</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>14440120</v>
       </c>
@@ -5553,25 +6154,25 @@
         <v>45841</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H54">
         <v>357</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>14508811</v>
       </c>
@@ -5579,25 +6180,25 @@
         <v>45845</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F55" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H55">
         <v>933</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="255" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:22" ht="255" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>14537143</v>
       </c>
@@ -5605,26 +6206,26 @@
         <v>45848</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H56">
         <v>447</v>
       </c>
-      <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="1:22" ht="289" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>14643406</v>
       </c>
@@ -5632,25 +6233,25 @@
         <v>45852</v>
       </c>
       <c r="C57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F57" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H57">
         <v>545</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="170" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>14821644</v>
       </c>
@@ -5658,25 +6259,25 @@
         <v>45861</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H58">
         <v>545</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>14857542</v>
       </c>
@@ -5684,25 +6285,25 @@
         <v>45862</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F59" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H59">
         <v>314</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="272" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:22" ht="272" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>14881179</v>
       </c>
@@ -5710,25 +6311,25 @@
         <v>45863</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H60">
         <v>536</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>15032798</v>
       </c>
@@ -5736,26 +6337,26 @@
         <v>45870</v>
       </c>
       <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
         <v>19</v>
       </c>
-      <c r="D61" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" t="s">
-        <v>21</v>
-      </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H61">
         <v>481</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>15039475</v>
       </c>
@@ -5763,26 +6364,26 @@
         <v>45870</v>
       </c>
       <c r="C62" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F62" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H62">
         <v>508</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="1:15" ht="323" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="323" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>15041914</v>
       </c>
@@ -5790,25 +6391,25 @@
         <v>45870</v>
       </c>
       <c r="C63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
         <v>19</v>
       </c>
-      <c r="D63" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" t="s">
-        <v>21</v>
-      </c>
       <c r="F63" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H63">
         <v>340</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="255" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:22" ht="255" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>15061560</v>
       </c>
@@ -5816,25 +6417,25 @@
         <v>45873</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H64">
         <v>671</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="170" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>15069211</v>
       </c>
@@ -5842,25 +6443,25 @@
         <v>45873</v>
       </c>
       <c r="C65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F65" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H65">
         <v>504</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>15262959</v>
       </c>
@@ -5868,26 +6469,26 @@
         <v>45882</v>
       </c>
       <c r="C66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H66">
         <v>748</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="1:15" ht="272" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="1:13" ht="272" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>15319561</v>
       </c>
@@ -5895,25 +6496,25 @@
         <v>45884</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F67" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H67">
         <v>365</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="340" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ht="340" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>15361347</v>
       </c>
@@ -5921,26 +6522,26 @@
         <v>45887</v>
       </c>
       <c r="C68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F68" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H68">
         <v>668</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="1:15" ht="306" x14ac:dyDescent="0.2">
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="1:13" ht="306" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>15429673</v>
       </c>
@@ -5948,25 +6549,25 @@
         <v>45891</v>
       </c>
       <c r="C69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F69" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H69">
         <v>445</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>15466630</v>
       </c>
@@ -5974,26 +6575,26 @@
         <v>45891</v>
       </c>
       <c r="C70" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F70" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H70">
         <v>370</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="1:15" ht="119" x14ac:dyDescent="0.2">
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>15508735</v>
       </c>
@@ -6001,26 +6602,26 @@
         <v>45893</v>
       </c>
       <c r="C71" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H71">
         <v>346</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>15569700</v>
       </c>
@@ -6028,25 +6629,25 @@
         <v>45898</v>
       </c>
       <c r="C72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F72" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H72">
         <v>313</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="388" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ht="388" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>15598588</v>
       </c>
@@ -6054,26 +6655,26 @@
         <v>45898</v>
       </c>
       <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
         <v>19</v>
       </c>
-      <c r="D73" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" t="s">
-        <v>21</v>
-      </c>
       <c r="F73" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H73">
         <v>430</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>15628315</v>
       </c>
@@ -6081,22 +6682,22 @@
         <v>45900</v>
       </c>
       <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
         <v>19</v>
       </c>
-      <c r="D74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E74" t="s">
-        <v>21</v>
-      </c>
       <c r="G74" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H74">
         <v>445</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="272" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="272" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>15677405</v>
       </c>
@@ -6104,26 +6705,26 @@
         <v>45902</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F75" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H75">
         <v>374</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>15720247</v>
       </c>
@@ -6131,26 +6732,26 @@
         <v>45904</v>
       </c>
       <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" t="s">
         <v>19</v>
       </c>
-      <c r="D76" t="s">
-        <v>20</v>
-      </c>
-      <c r="E76" t="s">
-        <v>21</v>
-      </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H76">
         <v>490</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="1:15" ht="356" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="1:13" ht="356" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>15740629</v>
       </c>
@@ -6158,25 +6759,25 @@
         <v>45905</v>
       </c>
       <c r="C77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H77">
         <v>451</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>15752875</v>
       </c>
@@ -6184,26 +6785,26 @@
         <v>45905</v>
       </c>
       <c r="C78" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F78" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H78">
         <v>363</v>
       </c>
-      <c r="O78" s="3"/>
-    </row>
-    <row r="79" spans="1:15" ht="119" x14ac:dyDescent="0.2">
+      <c r="M78" s="3"/>
+    </row>
+    <row r="79" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>15866942</v>
       </c>
@@ -6211,25 +6812,25 @@
         <v>45911</v>
       </c>
       <c r="C79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F79" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H79">
         <v>418</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="119" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15993109</v>
       </c>
@@ -6237,26 +6838,26 @@
         <v>45917</v>
       </c>
       <c r="C80" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F80" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H80">
         <v>363</v>
       </c>
-      <c r="O80" s="4"/>
-    </row>
-    <row r="81" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+      <c r="M80" s="4"/>
+    </row>
+    <row r="81" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16039722</v>
       </c>
@@ -6264,26 +6865,26 @@
         <v>45919</v>
       </c>
       <c r="C81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E81" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F81" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H81">
         <v>376</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>16175945</v>
       </c>
@@ -6291,25 +6892,25 @@
         <v>45925</v>
       </c>
       <c r="C82" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F82" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H82">
         <v>309</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="238" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ht="238" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>16367718</v>
       </c>
@@ -6317,26 +6918,26 @@
         <v>45934</v>
       </c>
       <c r="C83" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F83" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H83">
         <v>335</v>
       </c>
-      <c r="O83" s="4"/>
-    </row>
-    <row r="84" spans="1:15" ht="356" x14ac:dyDescent="0.2">
+      <c r="M83" s="4"/>
+    </row>
+    <row r="84" spans="1:13" ht="356" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>16391704</v>
       </c>
@@ -6344,25 +6945,25 @@
         <v>45936</v>
       </c>
       <c r="C84" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F84" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H84">
         <v>308</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="388" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ht="388" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>16751143</v>
       </c>
@@ -6370,25 +6971,25 @@
         <v>45952</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E85" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F85" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H85">
         <v>606</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="238" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ht="238" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>16983316</v>
       </c>
@@ -6396,26 +6997,26 @@
         <v>45964</v>
       </c>
       <c r="C86" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H86">
         <v>459</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>16989439</v>
       </c>
@@ -6423,26 +7024,26 @@
         <v>45964</v>
       </c>
       <c r="C87" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F87" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H87">
         <v>408</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>16991062</v>
       </c>
@@ -6450,26 +7051,26 @@
         <v>45964</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F88" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H88">
         <v>543</v>
       </c>
-      <c r="O88" s="4"/>
-    </row>
-    <row r="89" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+      <c r="M88" s="4"/>
+    </row>
+    <row r="89" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>17192243</v>
       </c>
@@ -6477,25 +7078,25 @@
         <v>45973</v>
       </c>
       <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" t="s">
         <v>19</v>
       </c>
-      <c r="D89" t="s">
-        <v>20</v>
-      </c>
-      <c r="E89" t="s">
-        <v>21</v>
-      </c>
       <c r="F89" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H89">
         <v>312</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>17682281</v>
       </c>
@@ -6503,25 +7104,25 @@
         <v>45994</v>
       </c>
       <c r="C90" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F90" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H90">
         <v>325</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>17803418</v>
       </c>
@@ -6529,26 +7130,26 @@
         <v>45990</v>
       </c>
       <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" t="s">
         <v>19</v>
       </c>
-      <c r="D91" t="s">
-        <v>20</v>
-      </c>
-      <c r="E91" t="s">
-        <v>21</v>
-      </c>
       <c r="F91" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H91">
         <v>636</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>17835768</v>
       </c>
@@ -6556,26 +7157,26 @@
         <v>45999</v>
       </c>
       <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" t="s">
         <v>19</v>
       </c>
-      <c r="D92" t="s">
-        <v>20</v>
-      </c>
-      <c r="E92" t="s">
-        <v>21</v>
-      </c>
       <c r="F92" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H92">
         <v>798</v>
       </c>
-      <c r="O92" s="4"/>
-    </row>
-    <row r="93" spans="1:15" ht="404" x14ac:dyDescent="0.2">
+      <c r="M92" s="4"/>
+    </row>
+    <row r="93" spans="1:13" ht="404" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>17905982</v>
       </c>
@@ -6583,26 +7184,26 @@
         <v>46001</v>
       </c>
       <c r="C93" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E93" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F93" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H93">
         <v>387</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="1:15" ht="388" x14ac:dyDescent="0.2">
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="1:13" ht="388" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>17908603</v>
       </c>
@@ -6610,26 +7211,26 @@
         <v>46001</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F94" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H94">
         <v>421</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="1:13" ht="289" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>17957498</v>
       </c>
@@ -6637,26 +7238,26 @@
         <v>45995</v>
       </c>
       <c r="C95" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" t="s">
         <v>19</v>
       </c>
-      <c r="D95" t="s">
-        <v>20</v>
-      </c>
-      <c r="E95" t="s">
-        <v>21</v>
-      </c>
       <c r="F95" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H95">
         <v>335</v>
       </c>
-      <c r="O95" s="4"/>
-    </row>
-    <row r="96" spans="1:15" ht="306" x14ac:dyDescent="0.2">
+      <c r="M95" s="4"/>
+    </row>
+    <row r="96" spans="1:13" ht="306" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>17971187</v>
       </c>
@@ -6664,25 +7265,25 @@
         <v>45988</v>
       </c>
       <c r="C96" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E96" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F96" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H96">
         <v>307</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="221" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>18056185</v>
       </c>
@@ -6690,26 +7291,26 @@
         <v>46006</v>
       </c>
       <c r="C97" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E97" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F97" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H97">
         <v>334</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="1:15" ht="289" x14ac:dyDescent="0.2">
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="1:13" ht="289" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>18391483</v>
       </c>
@@ -6717,26 +7318,26 @@
         <v>46022</v>
       </c>
       <c r="C98" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F98" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H98">
         <v>535</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>18423422</v>
       </c>
@@ -6744,26 +7345,26 @@
         <v>46024</v>
       </c>
       <c r="C99" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F99" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H99">
         <v>486</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>18535873</v>
       </c>
@@ -6771,26 +7372,26 @@
         <v>46029</v>
       </c>
       <c r="C100" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E100" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F100" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H100">
         <v>374</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="1:15" ht="204" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>18928428</v>
       </c>
@@ -6798,19 +7399,19 @@
         <v>46044</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E101" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F101" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H101">
         <v>441</v>

--- a/annotation_folder/annotated_results-nat.xlsx
+++ b/annotation_folder/annotated_results-nat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nataliechu/Desktop/CPSC 554/project/project_repo/annotation_folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B834904-B542-864C-A444-4E3E494B69B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A615A087-2B3F-1746-8220-880CC1DFFD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9780" yWindow="1760" windowWidth="37920" windowHeight="20780" xr2:uid="{678AFF50-194E-1844-9CF1-2C4B0496FC60}"/>
+    <workbookView xWindow="18320" yWindow="1640" windowWidth="37920" windowHeight="20780" xr2:uid="{678AFF50-194E-1844-9CF1-2C4B0496FC60}"/>
   </bookViews>
   <sheets>
     <sheet name="annotated_results-nat" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="410">
   <si>
     <t>Complaint ID</t>
   </si>
@@ -1765,6 +1765,117 @@
   </si>
   <si>
     <t>The money is still sitting at XXXX XXXX  and I have been waiting for XXXX XXXX. I opened a case with the police as well. On XX/XX/XXXX Capital One tried recall the money back again and they still have not responded...This lack of communication and resolution has caused me considerable concern</t>
+  </si>
+  <si>
+    <t>I then dispute the transaction with Cashapp on XX/XX/XXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I feel Cashapp is complicit in allowing thieves to scam unsuspecting citizens under the guise of running a legitimate business. </t>
+  </si>
+  <si>
+    <t>a hair stylist never showed up but my card was still charged and I provided the information that the appointment was missed and the dispute was denied because they said the service was completed</t>
+  </si>
+  <si>
+    <t>I followed the instructions the scammers gave me and converted my crypto back to dollars and made a contact card to their specification, then they had me text numbers to the contact card. The numbers was the money in my Venmo account and went out as XXXX XXXX transactions</t>
+  </si>
+  <si>
+    <t>I sent in screen shots of all the transactions, the contact card the scammers had me make with the phone number that my money was transferred to, and anything else I found like the web address for the scammers.</t>
+  </si>
+  <si>
+    <t>My money is gone, I was the victim</t>
+  </si>
+  <si>
+    <t>they took no accountability for their app not functioning and for the absence of any means of real communication to the company from the app with the exception of a chat bot that was useless. The could not track down my money or reverse it and they stopped trying to pursue the assailants, to the best of my knowledge.</t>
+  </si>
+  <si>
+    <t>resulting in a substantial financial loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Track and hold the scammers accountable, preventing them from defrauding others. </t>
+  </si>
+  <si>
+    <t>stole my money through XXXX transactions on the fraudulent platform XXXX</t>
+  </si>
+  <si>
+    <t>I gave cash to my XXXX  friend who lives in the same building and works at the same place and received a transfer via XXXX.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I have been suffering from mental distress and false suspicion for months. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I don't understand why I, as a consumer, am being harmed by a system error or security issue that occurred within XXXX itself. I'm really angry and in a difficult situation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">put those specific emails into my trash folder. I also had to change my email password. </t>
+  </si>
+  <si>
+    <t>these transactions were unauthorized, and my account had been hacked.</t>
+  </si>
+  <si>
+    <t>I know that I have provided Chime with all necessary information that I possibly could. The evidence is concrete and self explanatory that my account had been compromised. After 9 disputes filed, Chime continues to disregard all the evidences and not issue a full refund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I attempted to log into my Chime account. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Because I pay all of my bills through XXXX XXXX XXXX, reestablishing everything was a monumental task that took a months to resolve. In fact, at least XXXX of my creditors still have not been reestablished since the theft occurred in XX/XX/year&gt;. </t>
+  </si>
+  <si>
+    <t>was stopped since I had already closed my account by then...the thief had access to my checking account number and routing number, I am 99 % sure I know who the thief is...I have no doubt that XXXX already has or will commit crimes against other individuals if she is not stopped and brought to justice</t>
+  </si>
+  <si>
+    <t>I want to bring charges against her. Without cooperation from Capital One, she goes unpunished. I feel this is blatantly wrong and that Capital One is complicit in the commission of a crime...I have no doubt that XXXX already has or will commit crimes against other individuals if she is not stopped and brought to justice</t>
+  </si>
+  <si>
+    <t>My XXXX checking account was successfully hacked 3 times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I closed all of my accounts business and personal and opened new accounts, I reported the scam to XXXX XXXX XXXX XXXX XXXX  and the Police. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is deeply unfair in that the fraud relied on spoofing Well\'s Fargo\'s own number, causing me to TRUST the call. </t>
+  </si>
+  <si>
+    <t>We would like to trust Wells again by having them put more security in place and requesting a full reconsideration of this fraud case and reimbursement of the stolen XXXX</t>
+  </si>
+  <si>
+    <t>This Wells Fraudster walked me through a fake "security Process", and had me move my funds to an XXXX XXXX that I never used then instructed me to transfer it to a XXXX  card XXXX XXXX XXXX XXXX...I am XXXX and my husband is XXXX we were targeted as elders as we do not know about online bank transfers and moving money</t>
+  </si>
+  <si>
+    <t>I'm concerned there is fraud happening under my name and my email…I have tried to resolve this with customer service but they continue to tell me to do the following</t>
+  </si>
+  <si>
+    <t>I'm concerned that the emails are addressed correctly to me via my first name. There are back and forth transactions happening that I get email notifications on, but there is no email that ever asked for email verification. I'm concerned there is fraud happening under my name and my email</t>
+  </si>
+  <si>
+    <t>Fear</t>
+  </si>
+  <si>
+    <t>Impact statements on life quality</t>
+  </si>
+  <si>
+    <t>I don't have a Robinhood account, though this is my email</t>
+  </si>
+  <si>
+    <t>I was told that I would be arrested and jailed unless I sent bail payments via XXXX XXXX  by text message to a phone number that they provided, and was also told that I would be immediately arrested and jailed if I went to my local Sherriff 's Office to verify whether the call was genuine.</t>
+  </si>
+  <si>
+    <t>I would appreciate any assistance with persuading Bank of America to reverse these XXXX transactions, allowing me to recover my money</t>
+  </si>
+  <si>
+    <t>I realized that the call was a scam, and promptly called the support lines at both XXXX and Bank of America ( my personal bank ) to report the XXXX XXXX XXXX payments as the result of fraud, and to request that the transactions be reversed</t>
+  </si>
+  <si>
+    <t>I did authorize both payments with my debit card information, I authorized them because I was the victim of several serious crimes- including fraud, false arrest, and impersonating a law enforcement officer</t>
+  </si>
+  <si>
+    <t>I sent {$950.00} to my wife via XXXX  as a personal payment</t>
+  </si>
+  <si>
+    <t>XXXX  withdrew {$950.00} from my wifes account months before the dispute was completed by the card issuer, causing unnecessary financial harm</t>
+  </si>
+  <si>
+    <t>I respectfully request CFPBs assistance in directing Venmo to : Conduct a reinvestigation into the alleged dispute</t>
   </si>
 </sst>
 </file>
@@ -3255,7 +3366,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>11811866</v>
       </c>
@@ -3323,7 +3434,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>11817372</v>
       </c>
@@ -3664,7 +3775,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11966797</v>
       </c>
@@ -3936,7 +4047,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>12201830</v>
       </c>
@@ -4466,7 +4577,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>12614082</v>
       </c>
@@ -4732,7 +4843,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>13100288</v>
       </c>
@@ -5125,7 +5236,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>13562702</v>
       </c>
@@ -5193,7 +5304,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>13582132</v>
       </c>
@@ -5259,7 +5370,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>13586171</v>
       </c>
@@ -5641,7 +5752,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>14037359</v>
       </c>
@@ -5706,7 +5817,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>14038074</v>
       </c>
@@ -5961,7 +6072,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>14173829</v>
       </c>
@@ -6119,6 +6230,45 @@
       <c r="H52">
         <v>343</v>
       </c>
+      <c r="I52" s="15">
+        <v>0</v>
+      </c>
+      <c r="J52" s="15">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52" s="12">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="P52" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R52" s="5">
+        <v>2</v>
+      </c>
+      <c r="S52" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T52" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="U52">
+        <v>1</v>
+      </c>
+      <c r="V52" s="9" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="53" spans="1:22" ht="187" x14ac:dyDescent="0.2">
       <c r="A53">
@@ -6145,6 +6295,49 @@
       <c r="H53">
         <v>571</v>
       </c>
+      <c r="I53" s="15">
+        <v>4</v>
+      </c>
+      <c r="J53" s="15">
+        <v>1</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53" s="12">
+        <f>900+990</f>
+        <v>1890</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="P53" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R53" s="5">
+        <v>2</v>
+      </c>
+      <c r="S53" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T53" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="U53">
+        <v>2</v>
+      </c>
+      <c r="V53" s="9" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="54" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A54">
@@ -6171,6 +6364,46 @@
       <c r="H54">
         <v>357</v>
       </c>
+      <c r="I54" s="15">
+        <v>0</v>
+      </c>
+      <c r="J54" s="15">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54" s="12">
+        <f>1000+5000+16000+15000+10000+4000+5500+3600</f>
+        <v>60100</v>
+      </c>
+      <c r="N54">
+        <v>3</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="P54" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R54" s="5">
+        <v>2</v>
+      </c>
+      <c r="S54" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T54" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="U54">
+        <v>2</v>
+      </c>
+      <c r="V54" s="8" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="55" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A55">
@@ -6197,6 +6430,45 @@
       <c r="H55">
         <v>933</v>
       </c>
+      <c r="I55" s="15">
+        <v>0</v>
+      </c>
+      <c r="J55" s="15">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+      <c r="M55" s="12">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>3</v>
+      </c>
+      <c r="O55" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="P55" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R55" s="5">
+        <v>2</v>
+      </c>
+      <c r="S55" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T55" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="U55">
+        <v>1</v>
+      </c>
+      <c r="V55" s="9" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="56" spans="1:22" ht="255" x14ac:dyDescent="0.2">
       <c r="A56">
@@ -6223,7 +6495,48 @@
       <c r="H56">
         <v>447</v>
       </c>
-      <c r="M56" s="3"/>
+      <c r="I56" s="15">
+        <v>3</v>
+      </c>
+      <c r="J56" s="15">
+        <v>3</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N56" s="8">
+        <v>1</v>
+      </c>
+      <c r="O56" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="P56" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R56" s="5">
+        <v>2</v>
+      </c>
+      <c r="S56" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T56" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="U56">
+        <v>1</v>
+      </c>
+      <c r="V56" s="8" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="57" spans="1:22" ht="289" x14ac:dyDescent="0.2">
       <c r="A57">
@@ -6250,6 +6563,48 @@
       <c r="H57">
         <v>545</v>
       </c>
+      <c r="I57" s="15">
+        <v>3</v>
+      </c>
+      <c r="J57" s="15">
+        <v>1</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57" s="12">
+        <v>1400</v>
+      </c>
+      <c r="N57">
+        <v>3</v>
+      </c>
+      <c r="O57" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="P57" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="R57" s="5">
+        <v>2</v>
+      </c>
+      <c r="S57" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="T57" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57" s="8" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="58" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A58">
@@ -6276,6 +6631,48 @@
       <c r="H58">
         <v>545</v>
       </c>
+      <c r="I58" s="15">
+        <v>3</v>
+      </c>
+      <c r="J58" s="15">
+        <v>3</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="L58">
+        <v>2</v>
+      </c>
+      <c r="M58" s="12">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="P58" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="R58" s="5">
+        <v>2</v>
+      </c>
+      <c r="S58" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T58" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="U58">
+        <v>1</v>
+      </c>
+      <c r="V58" s="9" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="59" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A59">
@@ -6302,6 +6699,45 @@
       <c r="H59">
         <v>314</v>
       </c>
+      <c r="I59" s="15">
+        <v>3</v>
+      </c>
+      <c r="J59" s="15">
+        <v>3</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" s="12">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="P59" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="R59" s="5">
+        <v>2</v>
+      </c>
+      <c r="S59" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="T59" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59" s="8" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="60" spans="1:22" ht="272" x14ac:dyDescent="0.2">
       <c r="A60">
@@ -6328,6 +6764,48 @@
       <c r="H60">
         <v>536</v>
       </c>
+      <c r="I60" s="15">
+        <v>3</v>
+      </c>
+      <c r="J60" s="15">
+        <v>1</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60" s="12">
+        <v>5700</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="P60" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R60" s="5">
+        <v>2</v>
+      </c>
+      <c r="S60" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T60" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" s="9" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="61" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A61">
@@ -6354,7 +6832,45 @@
       <c r="H61">
         <v>481</v>
       </c>
-      <c r="M61" s="3"/>
+      <c r="I61" s="15">
+        <v>0</v>
+      </c>
+      <c r="J61" s="15">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61" s="3">
+        <v>950</v>
+      </c>
+      <c r="N61">
+        <v>2</v>
+      </c>
+      <c r="O61" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="P61" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="R61" s="5">
+        <v>2</v>
+      </c>
+      <c r="S61" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T61" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="U61">
+        <v>1</v>
+      </c>
+      <c r="V61" s="8" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="62" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A62">
